--- a/output/Guangxi/桂林市公共数据开放目录清单__.xlsx
+++ b/output/Guangxi/桂林市公共数据开放目录清单__.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,9 +570,7 @@
       <c r="M2" t="n">
         <v>49</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -588,7 +586,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局企业公示_许可变更信息</t>
+          <t>桂林市市场监督管理局分期认缴信息</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -598,7 +596,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>企业公示_许可变更信息</t>
+          <t>桂林市市场监督管理局分期认缴信息</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -613,16 +611,16 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2023-12-24</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12232</v>
+        <v>574812</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -631,18 +629,16 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>rdf,xml,csv,json,xls</t>
+          <t>csv,json,xls</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2659</v>
+        <v>530</v>
       </c>
       <c r="M3" t="n">
-        <v>37</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -658,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局投资人认缴详细</t>
+          <t>桂林市市场监督管理局企业公示_出资人实缴明细</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -668,7 +664,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局投资人认缴详细</t>
+          <t>企业公示_出资人实缴明细</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -678,7 +674,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -692,7 +688,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3626226</v>
+        <v>81690</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -701,18 +697,16 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3267</v>
+        <v>582</v>
       </c>
       <c r="M4" t="n">
-        <v>95</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -728,7 +722,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局简易案件当事人信息</t>
+          <t>桂林市市场监督管理局企业公示_许可变更信息</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -738,7 +732,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>简易案件当事人信息</t>
+          <t>企业公示_许可变更信息</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -748,21 +742,21 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>有条件开放</t>
+          <t>无条件开放</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>60060</v>
+        <v>12232</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -775,14 +769,12 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2895</v>
+        <v>2659</v>
       </c>
       <c r="M5" t="n">
-        <v>12</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -798,7 +790,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局委派代表信息</t>
+          <t>桂林市市场监督管理局投资人认缴详细</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -808,7 +800,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局委派代表信息</t>
+          <t>桂林市市场监督管理局投资人认缴详细</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -823,7 +815,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -832,7 +824,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>36645</v>
+        <v>3626226</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -841,18 +833,16 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>rdf,xml,csv,json,xls</t>
+          <t>csv,json,xls</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3175</v>
+        <v>3267</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -868,7 +858,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局清算成员信息</t>
+          <t>桂林市市场监督管理局简易案件当事人信息</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -878,7 +868,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局清算成员信息</t>
+          <t>简易案件当事人信息</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -888,21 +878,21 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>138644</v>
+        <v>60060</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -915,14 +905,12 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2616</v>
+        <v>2895</v>
       </c>
       <c r="M7" t="n">
-        <v>36</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -938,7 +926,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>桂林市注册号管理局简易案件案源信息</t>
+          <t>桂林市市场监督管理局委派代表信息</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -948,7 +936,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>桂林市注册号管理局简易案件案源信息</t>
+          <t>桂林市市场监督管理局委派代表信息</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -963,16 +951,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>21021</v>
+        <v>36645</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -985,14 +973,12 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2031</v>
+        <v>3175</v>
       </c>
       <c r="M8" t="n">
-        <v>33</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1008,17 +994,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局股权出质变更信息</t>
+          <t>桂林市市场监督管理局外资补充信息</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>市场监管</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局股权出质变更信息</t>
+          <t>桂林市市场监督管理局外资补充信息</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1028,12 +1014,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1042,7 +1028,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>342</v>
+        <v>123192</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1055,14 +1041,12 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3274</v>
+        <v>319</v>
       </c>
       <c r="M9" t="n">
-        <v>34</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1078,7 +1062,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局企业年报社会保险信息</t>
+          <t>桂林市市场监督管理局内资补充信息</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1088,7 +1072,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>企业年报社会保险信息</t>
+          <t>桂林市工商行政管理局内资补充信息</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1098,7 +1082,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1112,7 +1096,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>12087036</v>
+        <v>3804484</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1125,14 +1109,12 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2921</v>
+        <v>425</v>
       </c>
       <c r="M10" t="n">
-        <v>64</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1148,7 +1130,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局农专年报行政许可信息</t>
+          <t>桂林市市场监督管理局行政处罚信息</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1158,7 +1140,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局农专年报行政许可信息</t>
+          <t>桂林市市场监督管理局行政处罚信息</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1173,7 +1155,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1182,7 +1164,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2611</v>
+        <v>115905</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1195,14 +1177,12 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1992</v>
+        <v>240</v>
       </c>
       <c r="M11" t="n">
-        <v>34</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1218,7 +1198,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局企业年报对外提供保证担保信息</t>
+          <t>桂林市市场监督管理局企业公示_行政处罚变更</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1228,7 +1208,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局企业年报对外提供保证担保信息</t>
+          <t>桂林市工商行政管理局企业公示_行政处罚变更</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1238,12 +1218,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1252,7 +1232,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>46358</v>
+        <v>96</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1265,14 +1245,12 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1953</v>
+        <v>772</v>
       </c>
       <c r="M12" t="n">
-        <v>35</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1288,7 +1266,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局主要人员</t>
+          <t>桂林市市场监督管理局动产抵押变更信息</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1298,7 +1276,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>主要人员</t>
+          <t>动产抵押变更信息</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1308,7 +1286,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1322,7 +1300,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>15639325</v>
+        <v>455</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1331,18 +1309,16 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3856</v>
+        <v>627</v>
       </c>
       <c r="M13" t="n">
-        <v>101</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1358,7 +1334,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局企业公示_股东及出资修改信息</t>
+          <t>桂林市市场监督管理局个体吊销信息</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1368,7 +1344,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>企业公示_股东及出资修改信息</t>
+          <t>桂林市工商行政管理局个体吊销信息</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1378,21 +1354,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>有条件开放</t>
+          <t>无条件开放</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>26906</v>
+        <v>52355</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1405,14 +1381,12 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2746</v>
+        <v>738</v>
       </c>
       <c r="M14" t="n">
-        <v>31</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1428,7 +1402,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局动产抵押物信息</t>
+          <t>桂林市市场监督管理局12315投诉反馈信息</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1438,7 +1412,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局动产抵押物信息</t>
+          <t>桂林市市场监督管理局12315投诉反馈信息</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1448,12 +1422,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1462,7 +1436,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>29744</v>
+        <v>52740</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1475,14 +1449,12 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2699</v>
+        <v>323</v>
       </c>
       <c r="M15" t="n">
-        <v>40</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1498,7 +1470,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局集团变更信息</t>
+          <t>桂林市市场监督管理局清算成员信息</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1508,7 +1480,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局集团变更信息</t>
+          <t>桂林市市场监督管理局清算成员信息</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1518,7 +1490,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1532,7 +1504,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>408</v>
+        <v>138644</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1545,14 +1517,12 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3217</v>
+        <v>2616</v>
       </c>
       <c r="M16" t="n">
-        <v>34</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -1568,7 +1538,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局案源信息</t>
+          <t>桂林市市场监督管理局清算基本信息</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1578,7 +1548,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局案源信息</t>
+          <t>桂林市市场监督管理局清算基本信息</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1593,7 +1563,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1602,7 +1572,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>216048</v>
+        <v>50416</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1615,14 +1585,12 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3096</v>
+        <v>281</v>
       </c>
       <c r="M17" t="n">
-        <v>36</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -1638,17 +1606,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局企业年报修改信息</t>
+          <t>桂林市市场监督管理局个体年报修改信息</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>市场监管</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局企业年报修改信息</t>
+          <t>桂林市市场监督管理局个体年报修改信息</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1663,7 +1631,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1672,7 +1640,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2406192</v>
+        <v>402416</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1685,14 +1653,12 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3729</v>
+        <v>395</v>
       </c>
       <c r="M18" t="n">
-        <v>60</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -1708,7 +1674,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局迁出信息</t>
+          <t>桂林市市场监督管理局12315涉及客体信息</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1718,7 +1684,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局迁出信息</t>
+          <t>桂林市市场监督管理局12315涉及客体信息</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1728,12 +1694,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1742,7 +1708,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>100359</v>
+        <v>2275416</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1751,18 +1717,16 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>rdf,xml,csv,json,xls</t>
+          <t>csv,json,xls</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1920</v>
+        <v>348</v>
       </c>
       <c r="M19" t="n">
-        <v>35</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -1778,7 +1742,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局联络员信息</t>
+          <t>桂林市注册号管理局简易案件案源信息</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1788,7 +1752,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>桂林市工商行政管理局联络员信息</t>
+          <t>桂林市注册号管理局简易案件案源信息</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1803,7 +1767,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1812,7 +1776,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2514642</v>
+        <v>21021</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1821,18 +1785,16 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3091</v>
+        <v>2031</v>
       </c>
       <c r="M20" t="n">
-        <v>52</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -1848,7 +1810,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局简易注销信息</t>
+          <t>桂林市市场监督管理局当事人信息</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1858,7 +1820,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局简易注销信息</t>
+          <t>当事人信息</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1873,16 +1835,16 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>11660</v>
+        <v>618620</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1895,14 +1857,12 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3152</v>
+        <v>376</v>
       </c>
       <c r="M21" t="n">
-        <v>36</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -1918,17 +1878,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局电子营业执照</t>
+          <t>桂林市市场监督管理局股权出质变更信息</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>市场监管</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局电子营业执照</t>
+          <t>桂林市市场监督管理局股权出质变更信息</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1938,12 +1898,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1952,7 +1912,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2821680</v>
+        <v>342</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1961,18 +1921,16 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2674</v>
+        <v>3274</v>
       </c>
       <c r="M22" t="n">
-        <v>70</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -1988,7 +1946,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局企业名称信息</t>
+          <t>桂林市市场监督管理局12315调解信息</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1998,7 +1956,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>企业名称信息</t>
+          <t>桂林市市场监督管理局12315调解信息</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2008,12 +1966,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2022,7 +1980,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>9368224</v>
+        <v>84480</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2031,18 +1989,16 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6111</v>
+        <v>268</v>
       </c>
       <c r="M23" t="n">
-        <v>136</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2058,7 +2014,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局股权变更信息</t>
+          <t>桂林市市场监督管理局吊销企业法定代表人黑名单信息</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2068,7 +2024,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局股权变更信息</t>
+          <t>桂林市工商行政管理局吊销企业法定代表人黑名单信息</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2078,21 +2034,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2023-12-24</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>有条件开放</t>
+          <t>无条件开放</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2739</v>
+        <v>149104</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2105,14 +2061,12 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2897</v>
+        <v>378</v>
       </c>
       <c r="M24" t="n">
-        <v>10</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2128,7 +2082,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局历史法定代表人信息</t>
+          <t>桂林市市场监督管理局企业年报社会保险信息</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2138,7 +2092,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局历史法定代表人信息</t>
+          <t>企业年报社会保险信息</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2148,7 +2102,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2162,7 +2116,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>301070</v>
+        <v>12087036</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2171,18 +2125,16 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>rdf,xml,csv,json,xls</t>
+          <t>csv,json,xls</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2873</v>
+        <v>2921</v>
       </c>
       <c r="M25" t="n">
-        <v>36</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -2198,17 +2150,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>桂林市_市场监督局_进出口货物收货人备案</t>
+          <t>桂林市市场监督管理局12315登记信息</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>商业服务</t>
+          <t>市场监管</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>进出口货物收货人备案</t>
+          <t>桂林市市场监督管理局12315登记信息</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2218,21 +2170,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>有条件开放</t>
+          <t>无条件开放</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>116117136</v>
+        <v>4535544</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2245,14 +2197,12 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3917</v>
+        <v>447</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -2268,7 +2218,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局农专年报基本信息补充</t>
+          <t>桂林市市场监督管理局农专年报行政许可信息</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2278,7 +2228,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局农专年报基本信息补充</t>
+          <t>桂林市市场监督管理局农专年报行政许可信息</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2293,16 +2243,16 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>有条件开放</t>
+          <t>无条件开放</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>398430</v>
+        <v>2611</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2311,18 +2261,16 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3408</v>
+        <v>1992</v>
       </c>
       <c r="M27" t="n">
-        <v>36</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -2338,7 +2286,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局企业公示_出资人认缴明细</t>
+          <t>桂林市市场监督管理局企业年报对外提供保证担保信息</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2348,7 +2296,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局企业公示_出资人认缴明细</t>
+          <t>桂林市市场监督管理局企业年报对外提供保证担保信息</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2363,16 +2311,16 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>有条件开放</t>
+          <t>无条件开放</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>15360</v>
+        <v>46358</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2385,14 +2333,12 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2939</v>
+        <v>1953</v>
       </c>
       <c r="M28" t="n">
-        <v>33</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -2408,7 +2354,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局企业年报股东及出资信息</t>
+          <t>桂林市市场监督管理局12315分流信息</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2418,7 +2364,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>企业年报股东及出资信息</t>
+          <t>桂林市市场监督管理局12315分流信息</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2428,7 +2374,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2438,11 +2384,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>有条件开放</t>
+          <t>无条件开放</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>10061662</v>
+        <v>121464</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2451,18 +2397,16 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5187</v>
+        <v>472</v>
       </c>
       <c r="M29" t="n">
-        <v>120</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -2478,7 +2422,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局撤销登记信息</t>
+          <t>桂林市市场监督管理局主要人员</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2488,7 +2432,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局撤销登记信息</t>
+          <t>主要人员</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2498,12 +2442,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2512,7 +2456,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1800</v>
+        <v>15639325</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2521,18 +2465,16 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>rdf,xml,csv,json,xls</t>
+          <t>csv,json,xls</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9635</v>
+        <v>3856</v>
       </c>
       <c r="M30" t="n">
-        <v>36</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -2548,7 +2490,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局个体年报基本信息</t>
+          <t>桂林市市场监督管理局股权冻结信息</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2558,7 +2500,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>个体年报基本信息</t>
+          <t>股权冻结信息</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2578,11 +2520,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>有条件开放</t>
+          <t>无条件开放</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>42758364</v>
+        <v>115620</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2591,18 +2533,16 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>8490</v>
+        <v>343</v>
       </c>
       <c r="M31" t="n">
-        <v>208</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -2618,7 +2558,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局变更备案信息</t>
+          <t>桂林市市场监督管理局企业经营异常名录股东信息</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2628,7 +2568,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>变更备案信息</t>
+          <t>桂林市市场监督管理局企业经营异常名录股东信息</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2652,7 +2592,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5438187</v>
+        <v>376580</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2661,18 +2601,16 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4596</v>
+        <v>292</v>
       </c>
       <c r="M32" t="n">
-        <v>109</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -2688,7 +2626,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局企业年报基本信息</t>
+          <t>桂林市市场监督管理局企业公示_股东及出资修改信息</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2698,7 +2636,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>企业年报基本信息</t>
+          <t>企业公示_股东及出资修改信息</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2713,7 +2651,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2722,7 +2660,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>28727750</v>
+        <v>26906</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2731,18 +2669,16 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5296</v>
+        <v>2746</v>
       </c>
       <c r="M33" t="n">
-        <v>123</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -2758,7 +2694,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局个体变更信息</t>
+          <t>桂林市市场监督管理局动产抵押物信息</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2768,7 +2704,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局个体变更信息</t>
+          <t>桂林市市场监督管理局动产抵押物信息</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2783,7 +2719,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2792,7 +2728,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2145519</v>
+        <v>29744</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2801,18 +2737,16 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2973</v>
+        <v>2699</v>
       </c>
       <c r="M34" t="n">
-        <v>59</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -2828,7 +2762,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局个体年报行政许可信息</t>
+          <t>桂林市市场监督管理局12315涉及主体信息</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2838,7 +2772,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局个体年报行政许可信息</t>
+          <t>桂林市市场监督管理局12315涉及主体信息</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2862,7 +2796,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>870296</v>
+        <v>2456753</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2875,14 +2809,12 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1872</v>
+        <v>405</v>
       </c>
       <c r="M35" t="n">
-        <v>50</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -2898,7 +2830,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>桂林市_市场监督局_企业年报基本信息补充</t>
+          <t>桂林市市场监督管理局集团变更信息</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2908,7 +2840,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>企业年报基本信息补充</t>
+          <t>桂林市市场监督管理局集团变更信息</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2918,21 +2850,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>有条件开放</t>
+          <t>无条件开放</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6273069</v>
+        <v>408</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2941,18 +2873,16 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3700</v>
+        <v>3217</v>
       </c>
       <c r="M36" t="n">
-        <v>91</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -2968,7 +2898,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>桂林市简易案件基本信息ID管理局吊销信息</t>
+          <t>桂林市市场监督管理局企业公示_股权变更信息</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2978,7 +2908,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>吊销信息</t>
+          <t>桂林市市场监督管理局企业公示_股权变更信息</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2993,16 +2923,16 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>227822</v>
+        <v>132000</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3015,14 +2945,12 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2081</v>
+        <v>674</v>
       </c>
       <c r="M37" t="n">
-        <v>35</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -3038,7 +2966,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局农专年报基本信息</t>
+          <t>桂林市市场监督管理局股权冻结被执行人信息</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3048,7 +2976,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>农专年报基本信息</t>
+          <t>桂林市市场监督管理局股权冻结被执行人信息</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3058,12 +2986,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2021-11-26</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3072,7 +3000,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1159808</v>
+        <v>45120</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3081,18 +3009,16 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1952</v>
+        <v>241</v>
       </c>
       <c r="M38" t="n">
-        <v>38</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -3108,22 +3034,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>桂林市市场监督管理局企业外部审计情况</t>
+          <t>桂林市市场监督管理局案源信息</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>市场监管</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>桂林市工商行政管理局企业外部审计情况</t>
+          <t>桂林市市场监督管理局案源信息</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>桂林市工商业联合会</t>
+          <t>桂林市市场监督管理局</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3133,7 +3059,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3142,7 +3068,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5600</v>
+        <v>216048</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3155,14 +3081,12 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3675</v>
+        <v>3096</v>
       </c>
       <c r="M39" t="n">
-        <v>35</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -3178,41 +3102,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>桂林市营运车辆GPS信息</t>
+          <t>桂林市市场监督管理局12315举报反馈信息</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>市场监管</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>桂林市营运车辆GPS信息，包括位置经纬度，车牌等信息</t>
+          <t>桂林市市场监督管理局12315举报反馈信息</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>桂林市交通运输局</t>
+          <t>桂林市市场监督管理局</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>有条件开放</t>
+          <t>无条件开放</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>8823986680</v>
+        <v>21750</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3221,22 +3145,20 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4715</v>
+        <v>821</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -3248,27 +3170,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>桂林市营运车辆信息</t>
+          <t>桂林市市场监督管理局严重违法公告批量名单信息</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>市场监管</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>包括运营车辆车主，驾驶员，所属业主等信息</t>
+          <t>桂林市市场监督管理局严重违法公告批量名单信息</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>桂林市交通运输局</t>
+          <t>桂林市市场监督管理局</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3278,11 +3200,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>有条件开放</t>
+          <t>无条件开放</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>46548</v>
+        <v>28</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3291,20 +3213,3826 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>csv,json,xls</t>
+          <t>rdf,xml,csv,json,xls</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4387</v>
+        <v>290</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局企业年报修改信息</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局企业年报修改信息</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>2406192</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>3729</v>
+      </c>
+      <c r="M42" t="n">
+        <v>60</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局企业年报对外投资信息</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局企业年报对外投资信息</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>40728</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>233</v>
+      </c>
+      <c r="M43" t="n">
+        <v>44</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>桂林市市场监督行政管理局企业公示_行政处罚信息</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>桂林市市场监督行政管理局企业公示_行政处罚信息</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>2070</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>358</v>
+      </c>
+      <c r="M44" t="n">
+        <v>35</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局农专年报分支机构信息</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>桂林市工商行政管理局农专年报分支机构信息</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1602</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>348</v>
+      </c>
+      <c r="M45" t="n">
+        <v>35</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局行政处罚当事人信息</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局行政处罚当事人信息</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2023-12-25</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>94248</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>940</v>
+      </c>
+      <c r="M46" t="n">
+        <v>39</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局迁出信息</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局迁出信息</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2023-12-25</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>100359</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1920</v>
+      </c>
+      <c r="M47" t="n">
+        <v>35</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局案件基本信息</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>案件基本信息</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>696300</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>395</v>
+      </c>
+      <c r="M48" t="n">
+        <v>37</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局集团基本信息</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局集团基本信息</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2023-12-25</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>935</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>324</v>
+      </c>
+      <c r="M49" t="n">
+        <v>33</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局动产抵押被担保主债权信息</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>动产抵押被担保主债权信息</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>7956</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>377</v>
+      </c>
+      <c r="M50" t="n">
+        <v>36</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局联络员信息</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>桂林市工商行政管理局联络员信息</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>2514642</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>3091</v>
+      </c>
+      <c r="M51" t="n">
+        <v>52</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局简易注销信息</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局简易注销信息</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>11660</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>3152</v>
+      </c>
+      <c r="M52" t="n">
+        <v>36</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局电子营业执照</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局电子营业执照</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>2821680</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>2674</v>
+      </c>
+      <c r="M53" t="n">
+        <v>70</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局企业名称信息</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>企业名称信息</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2021-11-15</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>9368224</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>6111</v>
+      </c>
+      <c r="M54" t="n">
+        <v>136</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局财务负责人</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局财务负责人</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>1421010</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>368</v>
+      </c>
+      <c r="M55" t="n">
+        <v>51</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局小微企业名录基本信息</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局小微企业名录基本信息</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>4143000</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>586</v>
+      </c>
+      <c r="M56" t="n">
+        <v>93</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局12315督办信息</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局12315督办信息</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2023-12-25</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>88950</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>868</v>
+      </c>
+      <c r="M57" t="n">
+        <v>34</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局案件移送信息</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>桂林市工商行政管理局案件移送信息</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>230</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>291</v>
+      </c>
+      <c r="M58" t="n">
+        <v>32</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局个体经营者基本信息</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局个体经营者基本信息</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>11301786</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>427</v>
+      </c>
+      <c r="M59" t="n">
+        <v>12</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局企业年报股权变更信息</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局企业年报股权变更信息</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>232512</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>839</v>
+      </c>
+      <c r="M60" t="n">
+        <v>18</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局农专年报社会保险信息</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局农专年报社会保险信息</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>630315</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>277</v>
+      </c>
+      <c r="M61" t="n">
+        <v>35</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局股权变更信息</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局股权变更信息</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2021-11-30</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2023-12-24</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>2739</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>2897</v>
+      </c>
+      <c r="M62" t="n">
+        <v>10</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局严重违法失信企业详细信息</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>桂林市工商行政管理局严重违法失信企业详细信息</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>294140</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>268</v>
+      </c>
+      <c r="M63" t="n">
+        <v>46</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局历史法定代表人信息</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局历史法定代表人信息</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>301070</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>2873</v>
+      </c>
+      <c r="M64" t="n">
+        <v>36</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局经营异常公告批量名单信息</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局经营异常公告批量名单信息</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2023-12-24</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>409192</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>395</v>
+      </c>
+      <c r="M65" t="n">
+        <v>30</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>桂林市_市场监督局_进出口货物收货人备案</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>商业服务</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>进出口货物收货人备案</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>116117136</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>3917</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局农专年报基本信息补充</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局农专年报基本信息补充</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>398430</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>3408</v>
+      </c>
+      <c r="M67" t="n">
+        <v>36</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局农专补充信息</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局农专补充信息</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>131474</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>283</v>
+      </c>
+      <c r="M68" t="n">
+        <v>35</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局自然人出资信息</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局自然人出资信息</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>12612352</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>542</v>
+      </c>
+      <c r="M69" t="n">
+        <v>77</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局其他部门公示_行政处罚变更</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>桂林市工商行政管理局其他部门公示_行政处罚变更</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>2048</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>300</v>
+      </c>
+      <c r="M70" t="n">
+        <v>35</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局行政处罚决定书信息</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>桂林市工商行政管理局行政处罚决定书信息</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2021-11-15</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>40554</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>702</v>
+      </c>
+      <c r="M71" t="n">
+        <v>34</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局企业公示_出资人认缴明细</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局企业公示_出资人认缴明细</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>15360</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>2939</v>
+      </c>
+      <c r="M72" t="n">
+        <v>33</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局企业年报股东及出资信息</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>企业年报股东及出资信息</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>10061662</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>5187</v>
+      </c>
+      <c r="M73" t="n">
+        <v>120</v>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局动产抵押权人信息</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>动产抵押权人信息</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>6170</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>354</v>
+      </c>
+      <c r="M74" t="n">
+        <v>34</v>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局撤销登记信息</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局撤销登记信息</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>9635</v>
+      </c>
+      <c r="M75" t="n">
+        <v>36</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局个体撤销登记信息</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>桂林市工商行政管理局个体撤销登记信息</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>21231</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>302</v>
+      </c>
+      <c r="M76" t="n">
+        <v>35</v>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局严重违法失信企业名单</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>桂林市工商行政管理局严重违法失信企业名单</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>154125</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>268</v>
+      </c>
+      <c r="M77" t="n">
+        <v>39</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局个体年报基本信息</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>个体年报基本信息</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>42758364</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>8490</v>
+      </c>
+      <c r="M78" t="n">
+        <v>208</v>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局变更备案信息</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>变更备案信息</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>5438187</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>4596</v>
+      </c>
+      <c r="M79" t="n">
+        <v>109</v>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局企业年报基本信息</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>企业年报基本信息</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>28727750</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>5296</v>
+      </c>
+      <c r="M80" t="n">
+        <v>123</v>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局个体变更信息</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局个体变更信息</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>2145519</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>2973</v>
+      </c>
+      <c r="M81" t="n">
+        <v>59</v>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局个体年报行政许可信息</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局个体年报行政许可信息</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>870296</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>1872</v>
+      </c>
+      <c r="M82" t="n">
+        <v>50</v>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>桂林市_市场监督局_企业年报基本信息补充</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>企业年报基本信息补充</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>6273069</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>3700</v>
+      </c>
+      <c r="M83" t="n">
+        <v>91</v>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局商标案件维权人信息</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>桂林市工商行政管理局商标案件维权人信息</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>3435</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>418</v>
+      </c>
+      <c r="M84" t="n">
+        <v>34</v>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局分期实缴信息</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局分期实缴信息</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2023-12-24</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>836147</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>323</v>
+      </c>
+      <c r="M85" t="n">
+        <v>31</v>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局网站群自定义公告表</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局网站群自定义公告表</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2023-12-25</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>792</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>994</v>
+      </c>
+      <c r="M86" t="n">
+        <v>33</v>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局12315回访信息</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局12315回访信息</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>1240</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>237</v>
+      </c>
+      <c r="M87" t="n">
+        <v>37</v>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>桂林市简易案件基本信息ID管理局吊销信息</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>吊销信息</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2023-12-25</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>227822</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>2081</v>
+      </c>
+      <c r="M88" t="n">
+        <v>35</v>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局个体注销信息</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>个体注销信息</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>55400</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>422</v>
+      </c>
+      <c r="M89" t="n">
+        <v>78</v>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局农专年报基本信息</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>农专年报基本信息</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>1159808</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>1952</v>
+      </c>
+      <c r="M90" t="n">
+        <v>38</v>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局网站群公告附件信息表</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>网站群公告附件信息表</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>9334</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>467</v>
+      </c>
+      <c r="M91" t="n">
+        <v>33</v>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局简易案件基本信息</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>简易案件基本信息</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>42042</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>429</v>
+      </c>
+      <c r="M92" t="n">
+        <v>36</v>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局农专年报修改信息</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局农专年报修改信息</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2023-12-25</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>29808</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>993</v>
+      </c>
+      <c r="M93" t="n">
+        <v>31</v>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局12315申诉、举报回复信息</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>市场监管</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局12315申诉、举报回复信息</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>1014</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>567</v>
+      </c>
+      <c r="M94" t="n">
+        <v>35</v>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>桂林市市场监督管理局企业外部审计情况</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>桂林市工商行政管理局企业外部审计情况</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>桂林市工商业联合会</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>无条件开放</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>5600</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>rdf,xml,csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>3675</v>
+      </c>
+      <c r="M95" t="n">
+        <v>35</v>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>桂林市营运车辆GPS信息</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>桂林市营运车辆GPS信息，包括位置经纬度，车牌等信息</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>桂林市交通运输局</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>8823986680</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>4715</v>
+      </c>
+      <c r="M96" t="n">
+        <v>3</v>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>每季度</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>桂林市</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>桂林市营运车辆信息</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>包括运营车辆车主，驾驶员，所属业主等信息</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>桂林市交通运输局</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2022-10-09</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2023-12-23</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>46548</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>csv,json,xls</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>4387</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
         <is>
           <t>每季度</t>
         </is>
